--- a/data/file_generation/input/data_383/不愿意来院入住的.xlsx
+++ b/data/file_generation/input/data_383/不愿意来院入住的.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10125"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangxin1/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDAD1EC7-5718-9C48-B367-F1BD0D13BFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="141">
   <si>
     <t>序号</t>
   </si>
@@ -37,9 +31,15 @@
     <t>年龄</t>
   </si>
   <si>
+    <t>联系电话</t>
+  </si>
+  <si>
     <t>健康状况</t>
   </si>
   <si>
+    <t>住址</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -49,121 +49,127 @@
     <t>其他</t>
   </si>
   <si>
-    <t>user_1</t>
-  </si>
-  <si>
-    <t>user_2</t>
-  </si>
-  <si>
-    <t>user_3</t>
-  </si>
-  <si>
-    <t>user_4</t>
-  </si>
-  <si>
-    <t>user_5</t>
-  </si>
-  <si>
-    <t>user_6</t>
-  </si>
-  <si>
-    <t>user_7</t>
-  </si>
-  <si>
-    <t>user_8</t>
-  </si>
-  <si>
-    <t>user_9</t>
-  </si>
-  <si>
-    <t>user_10</t>
-  </si>
-  <si>
-    <t>user_11</t>
-  </si>
-  <si>
-    <t>user_12</t>
-  </si>
-  <si>
-    <t>user_13</t>
-  </si>
-  <si>
-    <t>user_14</t>
-  </si>
-  <si>
-    <t>user_15</t>
-  </si>
-  <si>
-    <t>user_16</t>
-  </si>
-  <si>
-    <t>user_17</t>
-  </si>
-  <si>
-    <t>user_18</t>
-  </si>
-  <si>
-    <t>user_19</t>
-  </si>
-  <si>
-    <t>user_20</t>
-  </si>
-  <si>
-    <t>user_21</t>
-  </si>
-  <si>
-    <t>user_22</t>
-  </si>
-  <si>
-    <t>user_23</t>
-  </si>
-  <si>
-    <t>user_24</t>
-  </si>
-  <si>
-    <t>user_25</t>
-  </si>
-  <si>
-    <t>user_26</t>
-  </si>
-  <si>
-    <t>user_27</t>
-  </si>
-  <si>
-    <t>user_28</t>
-  </si>
-  <si>
-    <t>user_29</t>
-  </si>
-  <si>
-    <t>user_30</t>
-  </si>
-  <si>
-    <t>user_31</t>
-  </si>
-  <si>
-    <t>user_32</t>
-  </si>
-  <si>
-    <t>user_33</t>
-  </si>
-  <si>
-    <t>user_34</t>
-  </si>
-  <si>
-    <t>user_35</t>
-  </si>
-  <si>
-    <t>user_36</t>
-  </si>
-  <si>
-    <t>user_37</t>
-  </si>
-  <si>
-    <t>user_38</t>
-  </si>
-  <si>
-    <t>user_39</t>
+    <t>usr-107</t>
+  </si>
+  <si>
+    <t>usr-110</t>
+  </si>
+  <si>
+    <t>usr-071</t>
+  </si>
+  <si>
+    <t>usr-049</t>
+  </si>
+  <si>
+    <t>usr-100</t>
+  </si>
+  <si>
+    <t>usr-001</t>
+  </si>
+  <si>
+    <t>usr-102</t>
+  </si>
+  <si>
+    <t>usr-120</t>
+  </si>
+  <si>
+    <t>usr-085</t>
+  </si>
+  <si>
+    <t>usr-126</t>
+  </si>
+  <si>
+    <t>usr-062</t>
+  </si>
+  <si>
+    <t>usr-042</t>
+  </si>
+  <si>
+    <t>usr-020</t>
+  </si>
+  <si>
+    <t>usr-127</t>
+  </si>
+  <si>
+    <t>usr-118</t>
+  </si>
+  <si>
+    <t>usr-039</t>
+  </si>
+  <si>
+    <t>usr-032</t>
+  </si>
+  <si>
+    <t>usr-051</t>
+  </si>
+  <si>
+    <t>usr-033</t>
+  </si>
+  <si>
+    <t>usr-006</t>
+  </si>
+  <si>
+    <t>usr-009</t>
+  </si>
+  <si>
+    <t>usr-080</t>
+  </si>
+  <si>
+    <t>usr-012</t>
+  </si>
+  <si>
+    <t>usr-035</t>
+  </si>
+  <si>
+    <t>usr-123</t>
+  </si>
+  <si>
+    <t>usr-048</t>
+  </si>
+  <si>
+    <t>usr-014</t>
+  </si>
+  <si>
+    <t>usr-083</t>
+  </si>
+  <si>
+    <t>usr-075</t>
+  </si>
+  <si>
+    <t>usr-003</t>
+  </si>
+  <si>
+    <t>usr-030</t>
+  </si>
+  <si>
+    <t>usr-025</t>
+  </si>
+  <si>
+    <t>usr-031</t>
+  </si>
+  <si>
+    <t>usr-027</t>
+  </si>
+  <si>
+    <t>usr-029</t>
+  </si>
+  <si>
+    <t>usr-044</t>
+  </si>
+  <si>
+    <t>usr-019</t>
+  </si>
+  <si>
+    <t>usr-076</t>
+  </si>
+  <si>
+    <t>usr-086</t>
+  </si>
+  <si>
+    <t>usr-056</t>
+  </si>
+  <si>
+    <t>usr-022</t>
   </si>
   <si>
     <t>男</t>
@@ -172,121 +178,121 @@
     <t>女</t>
   </si>
   <si>
-    <t>******195312080497</t>
-  </si>
-  <si>
-    <t>******1957061190023</t>
-  </si>
-  <si>
-    <t>******194711150611</t>
-  </si>
-  <si>
-    <t>******193710188226</t>
-  </si>
-  <si>
-    <t>******193709287577</t>
-  </si>
-  <si>
-    <t>******194909127492</t>
-  </si>
-  <si>
-    <t>******19410910050</t>
-  </si>
-  <si>
-    <t>******195702150745</t>
-  </si>
-  <si>
-    <t>******194212282724</t>
-  </si>
-  <si>
-    <t>******196507165740</t>
-  </si>
-  <si>
-    <t>******19410112255X</t>
-  </si>
-  <si>
-    <t>******193905210024</t>
-  </si>
-  <si>
-    <t>******193808120967</t>
-  </si>
-  <si>
-    <t>******195209200737</t>
-  </si>
-  <si>
-    <t>******195205050014</t>
-  </si>
-  <si>
-    <t>******196205066053</t>
-  </si>
-  <si>
-    <t>******194902090500</t>
-  </si>
-  <si>
-    <t>******195910297370</t>
-  </si>
-  <si>
-    <t>******194901090031</t>
-  </si>
-  <si>
-    <t>******193505027503</t>
-  </si>
-  <si>
-    <t>******193901040021</t>
-  </si>
-  <si>
-    <t>******195802253442</t>
-  </si>
-  <si>
-    <t>******19261004073X</t>
-  </si>
-  <si>
-    <t>******19540921499X</t>
-  </si>
-  <si>
-    <t>******196310100495</t>
-  </si>
-  <si>
-    <t>******19630714725X</t>
-  </si>
-  <si>
-    <t>******19570509307X</t>
-  </si>
-  <si>
-    <t>******193809170501</t>
-  </si>
-  <si>
-    <t>******196306020492</t>
-  </si>
-  <si>
-    <t>******194501210807</t>
-  </si>
-  <si>
-    <t>******195911270014</t>
-  </si>
-  <si>
-    <t>******195304072569</t>
-  </si>
-  <si>
-    <t>******196009023320</t>
-  </si>
-  <si>
-    <t>******196212226190</t>
-  </si>
-  <si>
-    <t>******195503022564</t>
-  </si>
-  <si>
-    <t>******193910040023</t>
-  </si>
-  <si>
-    <t>******1941107250069</t>
-  </si>
-  <si>
-    <t>******195011076339</t>
-  </si>
-  <si>
-    <t>******196111110498</t>
+    <t>ID-052</t>
+  </si>
+  <si>
+    <t>ID-072</t>
+  </si>
+  <si>
+    <t>ID-029</t>
+  </si>
+  <si>
+    <t>ID-007</t>
+  </si>
+  <si>
+    <t>ID-006</t>
+  </si>
+  <si>
+    <t>ID-032</t>
+  </si>
+  <si>
+    <t>ID-017</t>
+  </si>
+  <si>
+    <t>ID-068</t>
+  </si>
+  <si>
+    <t>ID-022</t>
+  </si>
+  <si>
+    <t>ID-001</t>
+  </si>
+  <si>
+    <t>ID-015</t>
+  </si>
+  <si>
+    <t>ID-012</t>
+  </si>
+  <si>
+    <t>ID-009</t>
+  </si>
+  <si>
+    <t>ID-048</t>
+  </si>
+  <si>
+    <t>ID-044</t>
+  </si>
+  <si>
+    <t>ID-091</t>
+  </si>
+  <si>
+    <t>ID-031</t>
+  </si>
+  <si>
+    <t>ID-083</t>
+  </si>
+  <si>
+    <t>ID-030</t>
+  </si>
+  <si>
+    <t>ID-005</t>
+  </si>
+  <si>
+    <t>ID-011</t>
+  </si>
+  <si>
+    <t>ID-076</t>
+  </si>
+  <si>
+    <t>ID-002</t>
+  </si>
+  <si>
+    <t>ID-053</t>
+  </si>
+  <si>
+    <t>ID-108</t>
+  </si>
+  <si>
+    <t>ID-107</t>
+  </si>
+  <si>
+    <t>ID-071</t>
+  </si>
+  <si>
+    <t>ID-010</t>
+  </si>
+  <si>
+    <t>ID-105</t>
+  </si>
+  <si>
+    <t>ID-024</t>
+  </si>
+  <si>
+    <t>ID-084</t>
+  </si>
+  <si>
+    <t>ID-049</t>
+  </si>
+  <si>
+    <t>ID-085</t>
+  </si>
+  <si>
+    <t>ID-097</t>
+  </si>
+  <si>
+    <t>ID-056</t>
+  </si>
+  <si>
+    <t>ID-014</t>
+  </si>
+  <si>
+    <t>ID-018</t>
+  </si>
+  <si>
+    <t>ID-038</t>
+  </si>
+  <si>
+    <t>ID-087</t>
   </si>
   <si>
     <t>残疾</t>
@@ -311,6 +317,120 @@
   </si>
   <si>
     <t>视力残疾</t>
+  </si>
+  <si>
+    <t>site-016</t>
+  </si>
+  <si>
+    <t>site-014</t>
+  </si>
+  <si>
+    <t>site-001</t>
+  </si>
+  <si>
+    <t>site-029</t>
+  </si>
+  <si>
+    <t>site-006</t>
+  </si>
+  <si>
+    <t>site-007</t>
+  </si>
+  <si>
+    <t>site-022</t>
+  </si>
+  <si>
+    <t>site-003</t>
+  </si>
+  <si>
+    <t>site-038</t>
+  </si>
+  <si>
+    <t>site-004</t>
+  </si>
+  <si>
+    <t>site-013</t>
+  </si>
+  <si>
+    <t>site-018</t>
+  </si>
+  <si>
+    <t>site-005</t>
+  </si>
+  <si>
+    <t>site-002</t>
+  </si>
+  <si>
+    <t>site-033</t>
+  </si>
+  <si>
+    <t>site-012</t>
+  </si>
+  <si>
+    <t>site-019</t>
+  </si>
+  <si>
+    <t>site-023</t>
+  </si>
+  <si>
+    <t>site-030</t>
+  </si>
+  <si>
+    <t>site-017</t>
+  </si>
+  <si>
+    <t>site-032</t>
+  </si>
+  <si>
+    <t>site-009</t>
+  </si>
+  <si>
+    <t>site-010</t>
+  </si>
+  <si>
+    <t>site-025</t>
+  </si>
+  <si>
+    <t>site-027</t>
+  </si>
+  <si>
+    <t>site-035</t>
+  </si>
+  <si>
+    <t>site-026</t>
+  </si>
+  <si>
+    <t>site-021</t>
+  </si>
+  <si>
+    <t>site-015</t>
+  </si>
+  <si>
+    <t>site-024</t>
+  </si>
+  <si>
+    <t>site-037</t>
+  </si>
+  <si>
+    <t>site-028</t>
+  </si>
+  <si>
+    <t>site-020</t>
+  </si>
+  <si>
+    <t>site-008</t>
+  </si>
+  <si>
+    <t>site-031</t>
+  </si>
+  <si>
+    <t>site-034</t>
+  </si>
+  <si>
+    <t>site-036</t>
+  </si>
+  <si>
+    <t>site-011</t>
   </si>
   <si>
     <t>低保</t>
@@ -322,12 +442,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -335,15 +455,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -389,25 +502,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -445,7 +550,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -479,7 +584,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -514,10 +618,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -690,14 +793,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
-  <cols>
-    <col min="4" max="4" width="41.6640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -725,900 +825,1170 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E2">
         <v>72</v>
       </c>
-      <c r="F2" t="s">
-        <v>89</v>
+      <c r="F2">
+        <v>18008180285</v>
+      </c>
+      <c r="G2" t="s">
+        <v>93</v>
       </c>
       <c r="H2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>101</v>
+      </c>
+      <c r="J2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E3">
         <v>65</v>
       </c>
-      <c r="F3" t="s">
-        <v>89</v>
+      <c r="F3">
+        <v>15228070618</v>
+      </c>
+      <c r="G3" t="s">
+        <v>93</v>
       </c>
       <c r="H3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>102</v>
+      </c>
+      <c r="J3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E4">
         <v>78</v>
       </c>
-      <c r="F4" t="s">
-        <v>90</v>
+      <c r="F4">
+        <v>15182876715</v>
+      </c>
+      <c r="G4" t="s">
+        <v>94</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>103</v>
+      </c>
+      <c r="J4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>88</v>
       </c>
-      <c r="F5" t="s">
-        <v>89</v>
+      <c r="F5">
+        <v>15983899153</v>
+      </c>
+      <c r="G5" t="s">
+        <v>93</v>
       </c>
       <c r="H5" t="s">
-        <v>97</v>
-      </c>
-      <c r="I5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>104</v>
+      </c>
+      <c r="J5" t="s">
+        <v>139</v>
+      </c>
+      <c r="K5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E6">
         <v>88</v>
       </c>
-      <c r="F6" t="s">
-        <v>89</v>
+      <c r="F6">
+        <v>15082415357</v>
+      </c>
+      <c r="G6" t="s">
+        <v>93</v>
       </c>
       <c r="H6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>105</v>
+      </c>
+      <c r="J6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E7">
         <v>76</v>
       </c>
-      <c r="F7" t="s">
-        <v>91</v>
+      <c r="F7">
+        <v>13419065846</v>
+      </c>
+      <c r="G7" t="s">
+        <v>95</v>
       </c>
       <c r="H7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>106</v>
+      </c>
+      <c r="J7" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E8">
         <v>84</v>
       </c>
-      <c r="F8" t="s">
-        <v>91</v>
+      <c r="F8">
+        <v>13568349673</v>
+      </c>
+      <c r="G8" t="s">
+        <v>95</v>
       </c>
       <c r="H8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>107</v>
+      </c>
+      <c r="J8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E9">
         <v>68</v>
       </c>
-      <c r="F9" t="s">
-        <v>89</v>
-      </c>
-      <c r="H9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="F9">
+        <v>13419098484</v>
+      </c>
+      <c r="G9" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E10">
         <v>83</v>
       </c>
-      <c r="F10" t="s">
-        <v>92</v>
+      <c r="F10">
+        <v>13778302368</v>
+      </c>
+      <c r="G10" t="s">
+        <v>96</v>
       </c>
       <c r="H10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>108</v>
+      </c>
+      <c r="J10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E11">
         <v>60</v>
       </c>
-      <c r="F11" t="s">
-        <v>89</v>
+      <c r="F11">
+        <v>13795695589</v>
+      </c>
+      <c r="G11" t="s">
+        <v>93</v>
       </c>
       <c r="H11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>109</v>
+      </c>
+      <c r="J11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E12">
         <v>84</v>
       </c>
-      <c r="F12" t="s">
-        <v>92</v>
+      <c r="F12">
+        <v>18228608140</v>
+      </c>
+      <c r="G12" t="s">
+        <v>96</v>
       </c>
       <c r="H12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>110</v>
+      </c>
+      <c r="J12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E13">
         <v>86</v>
       </c>
-      <c r="F13" t="s">
-        <v>92</v>
+      <c r="F13">
+        <v>18780814087</v>
+      </c>
+      <c r="G13" t="s">
+        <v>96</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>111</v>
+      </c>
+      <c r="J13" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E14">
         <v>84</v>
       </c>
-      <c r="F14" t="s">
-        <v>93</v>
+      <c r="F14">
+        <v>15882951719</v>
+      </c>
+      <c r="G14" t="s">
+        <v>97</v>
       </c>
       <c r="H14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>112</v>
+      </c>
+      <c r="J14" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E15">
         <v>73</v>
       </c>
-      <c r="F15" t="s">
-        <v>93</v>
+      <c r="F15">
+        <v>15328249218</v>
+      </c>
+      <c r="G15" t="s">
+        <v>97</v>
       </c>
       <c r="H15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>113</v>
+      </c>
+      <c r="J15" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E16">
         <v>73</v>
       </c>
-      <c r="F16" t="s">
-        <v>93</v>
+      <c r="F16">
+        <v>18282285646</v>
+      </c>
+      <c r="G16" t="s">
+        <v>97</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>114</v>
+      </c>
+      <c r="J16" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E17">
         <v>63</v>
       </c>
-      <c r="F17" t="s">
-        <v>93</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="F17">
+        <v>15984493329</v>
+      </c>
+      <c r="G17" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="J17" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E18">
         <v>76</v>
       </c>
-      <c r="F18" t="s">
-        <v>93</v>
+      <c r="F18">
+        <v>13079061185</v>
+      </c>
+      <c r="G18" t="s">
+        <v>97</v>
       </c>
       <c r="H18" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>115</v>
+      </c>
+      <c r="J18" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D19" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E19">
         <v>66</v>
       </c>
-      <c r="F19" t="s">
-        <v>93</v>
+      <c r="F19">
+        <v>13882872459</v>
+      </c>
+      <c r="G19" t="s">
+        <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>116</v>
+      </c>
+      <c r="J19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E20">
         <v>76</v>
       </c>
-      <c r="F20" t="s">
-        <v>89</v>
+      <c r="F20">
+        <v>15388389964</v>
+      </c>
+      <c r="G20" t="s">
+        <v>93</v>
       </c>
       <c r="H20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>117</v>
+      </c>
+      <c r="J20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E21">
         <v>91</v>
       </c>
-      <c r="F21" t="s">
-        <v>89</v>
+      <c r="F21">
+        <v>13668385101</v>
+      </c>
+      <c r="G21" t="s">
+        <v>93</v>
       </c>
       <c r="H21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>118</v>
+      </c>
+      <c r="J21" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C22" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E22">
         <v>86</v>
       </c>
-      <c r="F22" t="s">
-        <v>89</v>
+      <c r="F22">
+        <v>13702434461</v>
+      </c>
+      <c r="G22" t="s">
+        <v>93</v>
       </c>
       <c r="H22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>119</v>
+      </c>
+      <c r="J22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E23">
         <v>67</v>
       </c>
-      <c r="F23" t="s">
-        <v>89</v>
+      <c r="F23">
+        <v>18784840878</v>
+      </c>
+      <c r="G23" t="s">
+        <v>93</v>
       </c>
       <c r="H23" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>120</v>
+      </c>
+      <c r="J23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E24">
         <v>99</v>
       </c>
+      <c r="F24">
+        <v>13551460490</v>
+      </c>
       <c r="H24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>121</v>
+      </c>
+      <c r="J24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D25" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E25">
         <v>71</v>
       </c>
-      <c r="F25" t="s">
-        <v>94</v>
+      <c r="F25">
+        <v>19182854837</v>
+      </c>
+      <c r="G25" t="s">
+        <v>98</v>
       </c>
       <c r="H25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>122</v>
+      </c>
+      <c r="J25" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E26">
         <v>62</v>
       </c>
-      <c r="F26" t="s">
-        <v>89</v>
+      <c r="F26">
+        <v>18716478247</v>
+      </c>
+      <c r="G26" t="s">
+        <v>93</v>
       </c>
       <c r="H26" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>123</v>
+      </c>
+      <c r="J26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C27" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D27" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E27">
         <v>62</v>
       </c>
-      <c r="F27" t="s">
-        <v>89</v>
+      <c r="F27">
+        <v>18398866902</v>
+      </c>
+      <c r="G27" t="s">
+        <v>93</v>
       </c>
       <c r="H27" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>124</v>
+      </c>
+      <c r="J27" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E28">
         <v>68</v>
       </c>
-      <c r="F28" t="s">
-        <v>94</v>
+      <c r="F28">
+        <v>15082891911</v>
+      </c>
+      <c r="G28" t="s">
+        <v>98</v>
       </c>
       <c r="H28" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>125</v>
+      </c>
+      <c r="J28" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E29">
         <v>87</v>
       </c>
-      <c r="F29" t="s">
-        <v>94</v>
+      <c r="F29">
+        <v>13568165253</v>
+      </c>
+      <c r="G29" t="s">
+        <v>98</v>
       </c>
       <c r="H29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>126</v>
+      </c>
+      <c r="J29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E30">
         <v>62</v>
       </c>
-      <c r="F30" t="s">
-        <v>89</v>
+      <c r="F30">
+        <v>18682858408</v>
+      </c>
+      <c r="G30" t="s">
+        <v>93</v>
       </c>
       <c r="H30" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>127</v>
+      </c>
+      <c r="J30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D31" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E31">
         <v>80</v>
       </c>
-      <c r="F31" t="s">
-        <v>89</v>
+      <c r="F31">
+        <v>15082401558</v>
+      </c>
+      <c r="G31" t="s">
+        <v>93</v>
       </c>
       <c r="H31" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>128</v>
+      </c>
+      <c r="J31" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E32">
         <v>66</v>
       </c>
-      <c r="F32" t="s">
-        <v>89</v>
+      <c r="F32">
+        <v>18782863518</v>
+      </c>
+      <c r="G32" t="s">
+        <v>93</v>
       </c>
       <c r="H32" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>129</v>
+      </c>
+      <c r="J32" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E33">
         <v>72</v>
       </c>
-      <c r="F33" t="s">
-        <v>94</v>
+      <c r="F33">
+        <v>18136158610</v>
+      </c>
+      <c r="G33" t="s">
+        <v>98</v>
       </c>
       <c r="H33" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>130</v>
+      </c>
+      <c r="J33" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D34" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E34">
         <v>65</v>
       </c>
-      <c r="F34" t="s">
-        <v>94</v>
+      <c r="F34">
+        <v>18281899241</v>
+      </c>
+      <c r="G34" t="s">
+        <v>98</v>
       </c>
       <c r="H34" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>131</v>
+      </c>
+      <c r="J34" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D35" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E35">
         <v>63</v>
       </c>
-      <c r="F35" t="s">
-        <v>92</v>
+      <c r="F35">
+        <v>18808180198</v>
+      </c>
+      <c r="G35" t="s">
+        <v>96</v>
       </c>
       <c r="H35" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>132</v>
+      </c>
+      <c r="J35" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D36" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E36">
         <v>70</v>
       </c>
-      <c r="F36" t="s">
-        <v>92</v>
+      <c r="F36">
+        <v>18081510625</v>
+      </c>
+      <c r="G36" t="s">
+        <v>96</v>
       </c>
       <c r="H36" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>133</v>
+      </c>
+      <c r="J36" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E37">
         <v>83</v>
       </c>
-      <c r="F37" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="F37">
+        <v>13778386261</v>
+      </c>
+      <c r="G37" t="s">
+        <v>93</v>
+      </c>
+      <c r="H37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E38">
         <v>81</v>
       </c>
-      <c r="F38" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="F38">
+        <v>13548277492</v>
+      </c>
+      <c r="G38" t="s">
+        <v>99</v>
+      </c>
+      <c r="H38" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39">
+        <v>18228641888</v>
+      </c>
+      <c r="H39" t="s">
+        <v>136</v>
+      </c>
+      <c r="J39" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40">
+        <v>15228056599</v>
+      </c>
+      <c r="J40" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" t="s">
-        <v>48</v>
-      </c>
-      <c r="D39" t="s">
-        <v>87</v>
-      </c>
-      <c r="E39">
+      <c r="B41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41">
         <v>75</v>
       </c>
-      <c r="F39" t="s">
-        <v>96</v>
-      </c>
-      <c r="H39" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
-      <c r="A40">
+      <c r="F41">
+        <v>15881838473</v>
+      </c>
+      <c r="G41" t="s">
+        <v>100</v>
+      </c>
+      <c r="H41" t="s">
+        <v>137</v>
+      </c>
+      <c r="J41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B40" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40" t="s">
-        <v>48</v>
-      </c>
-      <c r="D40" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40">
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42">
         <v>63</v>
       </c>
-      <c r="F40" t="s">
-        <v>89</v>
-      </c>
-      <c r="H40" t="s">
-        <v>97</v>
+      <c r="F42">
+        <v>13518250173</v>
+      </c>
+      <c r="G42" t="s">
+        <v>93</v>
+      </c>
+      <c r="H42" t="s">
+        <v>138</v>
+      </c>
+      <c r="J42" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1787,13 +2157,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C641DA82-DCE3-4476-83ED-71B55E0751F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0765FA9-EB8B-41A0-8102-629FAA492B2F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DB34253-0DE5-4CDB-89A9-2C0E0EB0091C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42AC35FF-BED9-463C-A454-440A0382849B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC0CCD0-4EEC-4340-8558-0E99D01CB3A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD8BB83C-17C0-4A7B-91ED-4322B93DB2F4}"/>
 </file>